--- a/04-pinecastle-software-grc-program/03-third-party-risk-management/artifacts/Pinecastle-Third-Party-Risk-Assessment.xlsx
+++ b/04-pinecastle-software-grc-program/03-third-party-risk-management/artifacts/Pinecastle-Third-Party-Risk-Assessment.xlsx
@@ -820,6 +820,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -1021,7 +1022,7 @@
         </is>
       </c>
       <c r="B9" s="55" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D9" s="31">
         <f>'Scorecard'!A7</f>
@@ -1066,6 +1067,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
@@ -1140,7 +1142,7 @@
         </is>
       </c>
       <c r="G13" s="57" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
@@ -1180,7 +1182,7 @@
         </is>
       </c>
       <c r="G14" s="58" t="n">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
@@ -1220,7 +1222,7 @@
         </is>
       </c>
       <c r="G15" s="58" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="H15" s="31" t="inlineStr">
         <is>
@@ -1260,7 +1262,7 @@
         </is>
       </c>
       <c r="G16" s="58" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="H16" s="31" t="inlineStr">
         <is>
@@ -1300,7 +1302,7 @@
         </is>
       </c>
       <c r="G17" s="59" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="H17" s="32" t="inlineStr">
         <is>
@@ -1349,6 +1351,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -1476,7 +1479,7 @@
         </is>
       </c>
       <c r="D8" s="60" t="n">
-        <v>46625</v>
+        <v>46626</v>
       </c>
     </row>
     <row r="9">
@@ -1562,7 +1565,7 @@
         </is>
       </c>
       <c r="D12" s="55" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
   </sheetData>
@@ -2855,7 +2858,7 @@
         </is>
       </c>
       <c r="I2" s="57" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="J2" s="30" t="inlineStr">
         <is>
@@ -2910,7 +2913,7 @@
         </is>
       </c>
       <c r="I3" s="58" t="n">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
@@ -2965,7 +2968,7 @@
         </is>
       </c>
       <c r="I4" s="58" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="J4" s="31" t="inlineStr">
         <is>
@@ -3020,7 +3023,7 @@
         </is>
       </c>
       <c r="I5" s="58" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="J5" s="31" t="inlineStr">
         <is>
@@ -3075,7 +3078,7 @@
         </is>
       </c>
       <c r="I6" s="59" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="J6" s="32" t="inlineStr">
         <is>
@@ -3177,7 +3180,7 @@
         </is>
       </c>
       <c r="D2" s="57" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="E2" s="30" t="inlineStr">
         <is>
@@ -3216,7 +3219,7 @@
         </is>
       </c>
       <c r="D3" s="58" t="n">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
@@ -3255,7 +3258,7 @@
         </is>
       </c>
       <c r="D4" s="58" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="E4" s="31" t="inlineStr">
         <is>
@@ -3294,7 +3297,7 @@
         </is>
       </c>
       <c r="D5" s="58" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
@@ -3333,7 +3336,7 @@
         </is>
       </c>
       <c r="D6" s="59" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
@@ -3388,6 +3391,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -3514,7 +3518,7 @@
         </is>
       </c>
       <c r="D8" s="60" t="n">
-        <v>46625</v>
+        <v>46626</v>
       </c>
     </row>
     <row r="9">
@@ -3534,7 +3538,7 @@
         </is>
       </c>
       <c r="D9" s="60" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="10">
